--- a/sale-analysis-excel-project.xlsx
+++ b/sale-analysis-excel-project.xlsx
@@ -2,30 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8fcef56c8843fd0e/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="199" documentId="8_{F88FAA05-9332-46D7-91C1-F3D58DFB6115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B34C739-873A-4B25-B02C-FF533F708E7B}"/>
+  <xr:revisionPtr revIDLastSave="271" documentId="8_{F88FAA05-9332-46D7-91C1-F3D58DFB6115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1A9E394-FE50-44B7-8F42-8D48FF0CE1E8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="883" activeTab="7" xr2:uid="{25F908D8-DA46-4402-8093-230AFF80129F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="883" activeTab="2" xr2:uid="{25F908D8-DA46-4402-8093-230AFF80129F}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
     <sheet name="Analysis" sheetId="5" r:id="rId2"/>
-    <sheet name="Pivot_Region_Sales" sheetId="6" r:id="rId3"/>
-    <sheet name="Chart_Region_Sales" sheetId="8" r:id="rId4"/>
-    <sheet name="Pivot_Category_Profit" sheetId="7" r:id="rId5"/>
-    <sheet name="Chart_Category_Profit" sheetId="9" r:id="rId6"/>
-    <sheet name="Pivot_Sales_Over_Time" sheetId="11" r:id="rId7"/>
-    <sheet name="Chart_Sales_Over_Time" sheetId="12" r:id="rId8"/>
-    <sheet name="Insights" sheetId="2" r:id="rId9"/>
+    <sheet name="Dashboard" sheetId="13" r:id="rId3"/>
+    <sheet name="Region_Analysis" sheetId="6" r:id="rId4"/>
+    <sheet name="Category_Analysis" sheetId="7" r:id="rId5"/>
+    <sheet name="Sales_Analysis" sheetId="11" r:id="rId6"/>
+    <sheet name="Insights" sheetId="2" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId10"/>
+    <pivotCache cacheId="0" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -47,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="59">
   <si>
     <t>Order Date</t>
   </si>
@@ -222,6 +220,9 @@
   <si>
     <t>Furniture products generated the highest total profit, indicating stronger margins compared to other categories.</t>
   </si>
+  <si>
+    <t>Sales Performance Dashboard</t>
+  </si>
 </sst>
 </file>
 
@@ -231,7 +232,7 @@
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="m/d;@"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -263,6 +264,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -284,7 +293,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -306,6 +315,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -337,8 +349,8 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[sale-analysis-excel-project.xlsx]Pivot_Region_Sales!PivotTable1</c:name>
-    <c:fmtId val="2"/>
+    <c:name>[sale-analysis-excel-project.xlsx]Region_Analysis!PivotTable1</c:name>
+    <c:fmtId val="8"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
@@ -362,7 +374,1347 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Total Sales by Region </a:t>
+              <a:t>Sales by Region</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Region_Analysis!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Region_Analysis!$A$4:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>West</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Region_Analysis!$B$4:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0.00_);[Red]\("$"#,##0.00\)</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5240</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2390</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2505</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2720</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BB4A-46E0-AC30-2C8A312FF88F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1040576704"/>
+        <c:axId val="1040577184"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1040576704"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1040577184"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1040577184"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1040576704"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[sale-analysis-excel-project.xlsx]Category_Analysis!PivotTable1</c:name>
+    <c:fmtId val="24"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Profit by Category</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Category_Analysis!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Category_Analysis!$A$4:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Furniture</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Office Supplies</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Technology</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Category_Analysis!$B$4:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0.00_);[Red]\("$"#,##0.00\)</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1985</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1730</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-054A-4979-9243-044C59525C60}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="665515760"/>
+        <c:axId val="665517200"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="665515760"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="665517200"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="665517200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="665515760"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[sale-analysis-excel-project.xlsx]Sales_Analysis!PivotTable6</c:name>
+    <c:fmtId val="5"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Sales Over Time</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.49538666666666664"/>
+          <c:y val="0.17778402699662543"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sales_Analysis!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sales_Analysis!$A$4:$A$34</c:f>
+              <c:strCache>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>1/1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1/2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1/3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1/4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1/5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1/6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1/7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1/8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1/9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1/10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1/11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1/12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1/13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1/14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1/15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1/16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1/17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1/18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1/19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1/20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1/21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1/22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1/23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1/24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1/25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1/26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1/27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1/28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1/29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1/30</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sales_Analysis!$B$4:$B$34</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0.00_);[Red]\("$"#,##0.00\)</c:formatCode>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1100</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>950</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>275</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F189-4612-8985-93BFB5EC95C5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="665467120"/>
+        <c:axId val="665468560"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="665467120"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="665468560"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="665468560"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="665467120"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[sale-analysis-excel-project.xlsx]Region_Analysis!PivotTable1</c:name>
+    <c:fmtId val="12"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Sales by Region</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -510,437 +1862,8 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Pivot_Region_Sales!$B$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Pivot_Region_Sales!$A$4:$A$8</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>East</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>North</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>South</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>West</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Pivot_Region_Sales!$B$4:$B$8</c:f>
-              <c:numCache>
-                <c:formatCode>"$"#,##0.00_);[Red]\("$"#,##0.00\)</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>5240</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2390</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2505</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2720</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-05BF-4EDB-8456-2517B78E385A}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="102540496"/>
-        <c:axId val="102540016"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="102540496"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="102540016"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="102540016"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="102540496"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[sale-analysis-excel-project.xlsx]Pivot_Category_Profit!PivotTable1</c:name>
-    <c:fmtId val="23"/>
-  </c:pivotSource>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Total Profit by Product Category</a:t>
-            </a:r>
-          </a:p>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
       <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
+        <c:idx val="2"/>
         <c:spPr>
           <a:solidFill>
             <a:schemeClr val="accent1"/>
@@ -999,15 +1922,15 @@
     <c:plotArea>
       <c:layout/>
       <c:barChart>
-        <c:barDir val="bar"/>
-        <c:grouping val="stacked"/>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Pivot_Category_Profit!$B$3</c:f>
+              <c:f>Region_Analysis!$B$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1028,42 +1951,48 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Pivot_Category_Profit!$A$4:$A$7</c:f>
+              <c:f>Region_Analysis!$A$4:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>Furniture</c:v>
+                  <c:v>East</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Office Supplies</c:v>
+                  <c:v>North</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Technology</c:v>
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>West</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Pivot_Category_Profit!$B$4:$B$7</c:f>
+              <c:f>Region_Analysis!$B$4:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>"$"#,##0.00_);[Red]\("$"#,##0.00\)</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>1985</c:v>
+                  <c:v>5240</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>115</c:v>
+                  <c:v>2390</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1730</c:v>
+                  <c:v>2505</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2720</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-BF30-4943-8B20-54FBCC9D0DFE}"/>
+              <c16:uniqueId val="{00000000-C1CF-4E2A-838C-DEDD596CD632}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1075,688 +2004,13 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:overlap val="100"/>
-        <c:axId val="110795280"/>
-        <c:axId val="107982976"/>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1040576704"/>
+        <c:axId val="1040577184"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="110795280"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="107982976"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="107982976"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="110795280"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[sale-analysis-excel-project.xlsx]Pivot_Sales_Over_Time!PivotTable6</c:name>
-    <c:fmtId val="4"/>
-  </c:pivotSource>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Sales Over Time</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="28575" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="5"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:ln w="28575" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="5"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Pivot_Sales_Over_Time!$B$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Pivot_Sales_Over_Time!$A$4:$A$34</c:f>
-              <c:strCache>
-                <c:ptCount val="30"/>
-                <c:pt idx="0">
-                  <c:v>1/1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1/2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1/3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1/4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1/5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1/6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1/7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1/8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1/9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1/10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1/11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1/12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1/13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1/14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1/15</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>1/16</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1/17</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1/18</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1/19</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>1/20</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>1/21</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>1/22</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1/23</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>1/24</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>1/25</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>1/26</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>1/27</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>1/28</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>1/29</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>1/30</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Pivot_Sales_Over_Time!$B$4:$B$34</c:f>
-              <c:numCache>
-                <c:formatCode>"$"#,##0.00_);[Red]\("$"#,##0.00\)</c:formatCode>
-                <c:ptCount val="30"/>
-                <c:pt idx="0">
-                  <c:v>450</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1200</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>75</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>300</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>650</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>800</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>500</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>600</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>900</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>55</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>700</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1100</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>1000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>150</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>400</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>200</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>1300</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>250</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>60</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>550</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>950</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>45</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>275</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>180</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>30</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-ED97-4397-8814-D52DC24F1740}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="128482736"/>
-        <c:axId val="128474096"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="128482736"/>
+        <c:axId val="1040576704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1799,7 +2053,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="128474096"/>
+        <c:crossAx val="1040577184"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1807,7 +2061,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="128474096"/>
+        <c:axId val="1040577184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1858,7 +2112,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="128482736"/>
+        <c:crossAx val="1040576704"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1870,37 +2124,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -1937,13 +2160,15 @@
       <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
   <c:extLst>
     <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
       <c14:pivotOptions>
         <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
         <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
@@ -2076,6 +2301,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -2580,7 +2845,7 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -3085,7 +3350,7 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -3193,6 +3458,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -3203,6 +3473,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -3234,6 +3509,9 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3587,46 +3865,692 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{ED3C0195-D2D3-4FDE-B820-7B1C5478958E}">
-  <sheetPr/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</chartsheet>
-</file>
-
-<file path=xl/chartsheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{8D032CD1-08B7-461D-8862-7F451BC3D738}">
-  <sheetPr/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</chartsheet>
-</file>
-
-<file path=xl/chartsheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{22F88058-A9CA-4B3D-AA82-5090C2733908}">
-  <sheetPr/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</chartsheet>
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="8665221" cy="6288186"/>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>317389</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>88631</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE1993E4-C947-865F-CB10-EA4BB29D0F79}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="190500"/>
+          <a:ext cx="4584589" cy="2755631"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>155575</xdr:rowOff>
+    </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
+        <xdr:cNvPr id="6" name="Chart 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71E57E69-5056-3918-09EC-1B28A87C73D6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{513B20FF-E21C-590B-906E-0C60A9841BEB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>603250</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{471DDBDE-C709-62E2-514B-8EC84D3AE66E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>98425</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5855086F-6ED4-F161-83C0-9F7BFD8BC6B0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>136525</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B07DC3E-791E-456B-A004-DE4657FCA317}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks noGrp="1"/>
+          <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -3640,74 +4564,110 @@
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="8665221" cy="6288186"/>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{623AF8D4-F995-ED49-D500-49E991ADE25A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks noGrp="1"/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="8665221" cy="6288186"/>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>341828</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>140484</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{500D72B2-E101-2CA0-937A-721CD0C2AE19}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C3E69F0-7FC6-F9D0-006F-8BA87EE8EC6E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks noGrp="1"/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2409825" y="381000"/>
+          <a:ext cx="5218628" cy="3188484"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
-  </xdr:absoluteAnchor>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>21056</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>89844</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{453E7526-0B2C-CFEB-2E2A-A21A30E5B708}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2162175" y="1095375"/>
+          <a:ext cx="9955631" cy="3566469"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4093,7 +5053,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EFE185C3-CB33-44FF-BF29-49ED15FAA33D}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EFE185C3-CB33-44FF-BF29-49ED15FAA33D}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
   <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField numFmtId="164" showAll="0"/>
@@ -4138,8 +5098,17 @@
   <dataFields count="1">
     <dataField name="Sum of Sales" fld="4" baseField="0" baseItem="0" numFmtId="8"/>
   </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="2" format="1" series="1">
+  <chartFormats count="2">
+    <chartFormat chart="8" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -4162,7 +5131,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B273420F-831B-44A4-8B9C-386DC79972C1}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="24">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B273420F-831B-44A4-8B9C-386DC79972C1}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28">
   <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField numFmtId="164" showAll="0"/>
@@ -4204,7 +5173,7 @@
     <dataField name="Sum of Profit" fld="6" baseField="0" baseItem="0" numFmtId="8"/>
   </dataFields>
   <chartFormats count="1">
-    <chartFormat chart="23" format="1" series="1">
+    <chartFormat chart="24" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -4227,7 +5196,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F4F74893-6C3A-4F20-8089-BBDA590B37CE}" name="PivotTable6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F4F74893-6C3A-4F20-8089-BBDA590B37CE}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
   <location ref="A3:B34" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField axis="axisRow" numFmtId="164" showAll="0">
@@ -4377,7 +5346,7 @@
     <dataField name="Sum of Sales" fld="4" baseField="0" baseItem="0" numFmtId="8"/>
   </dataFields>
   <chartFormats count="1">
-    <chartFormat chart="4" format="1" series="1">
+    <chartFormat chart="5" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -6166,6 +7135,64 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23C59116-57C4-45AF-B7CE-6CABBFD3CDEE}">
+  <dimension ref="B1:T2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+    </row>
+    <row r="2" spans="2:20" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:T2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CD4EBBA-B0A1-413D-A1A7-156D1637FD15}">
   <dimension ref="A3:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6224,10 +7251,11 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{537B1163-98C3-43A3-99C4-1442714D179D}">
   <dimension ref="A3:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6278,10 +7306,11 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08771650-A1DE-472A-B441-464311261577}">
   <dimension ref="A3:B34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6548,10 +7577,11 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{497FA8F9-F4A0-4A3F-BDD6-88E71FED6893}">
   <dimension ref="A1:A14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
